--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/phi-4/metrics_default_vs_simple.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/phi-4/metrics_default_vs_simple.xlsx
@@ -420,22 +420,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.4444444444444444</v>
+        <v>0.4435483870967742</v>
       </c>
       <c r="B2">
-        <v>0.1111111111111111</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.4468085106382979</v>
+        <v>0.4295774647887324</v>
       </c>
       <c r="D2">
-        <v>0.5777777777777777</v>
+        <v>0.5955882352941176</v>
       </c>
       <c r="E2">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G2">
         <v>6</v>
